--- a/output/pdf_financials_xlsx/MAN.P.xlsx
+++ b/output/pdf_financials_xlsx/MAN.P.xlsx
@@ -2638,13 +2638,13 @@
         <v>0</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0</v>
+        <v>0.039406</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>0</v>
+        <v>0.039406</v>
       </c>
       <c r="F92" s="3" t="n">
-        <v>0</v>
+        <v>0.039406</v>
       </c>
     </row>
     <row r="93">
@@ -3974,7 +3974,11 @@
           <t>Reserve 4</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr"/>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E9" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/MAN.P.xlsx
+++ b/output/pdf_financials_xlsx/MAN.P.xlsx
@@ -669,7 +669,7 @@
         <v>0.04336</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>0.011713</v>
+        <v>0.036781</v>
       </c>
     </row>
     <row r="11">
@@ -717,13 +717,13 @@
         </is>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>0.012117</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>0</v>
+        <v>0.011585</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>0</v>
+        <v>0.006087</v>
       </c>
     </row>
     <row r="13">
@@ -1125,10 +1125,10 @@
         </is>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-0.16851</v>
+        <v>-0.180627</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>-0.031775</v>
+        <v>-0.04336</v>
       </c>
       <c r="F27" s="1" t="inlineStr">
         <is>
@@ -1179,10 +1179,10 @@
         </is>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-0.16851</v>
+        <v>-0.180627</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>-0.031775</v>
+        <v>-0.04336</v>
       </c>
       <c r="F29" s="1" t="inlineStr">
         <is>
@@ -1296,7 +1296,7 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.156797</v>
       </c>
       <c r="C34" s="3" t="n">
         <v>0.065648</v>
@@ -1340,7 +1340,7 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.156797</v>
       </c>
       <c r="C36" s="3" t="n">
         <v>0.065648</v>
@@ -1604,7 +1604,7 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>0.156797</v>
+        <v>0</v>
       </c>
       <c r="C48" s="3" t="n">
         <v>0</v>
@@ -4518,7 +4518,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E23" s="5" t="n">
@@ -5833,7 +5833,7 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>TotalExpenses</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -5876,7 +5876,7 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
@@ -6294,7 +6294,7 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">

--- a/output/pdf_financials_xlsx/MAN.P.xlsx
+++ b/output/pdf_financials_xlsx/MAN.P.xlsx
@@ -5320,7 +5320,11 @@
           <t>Shares issued for cash 4</t>
         </is>
       </c>
-      <c r="D43" t="inlineStr"/>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E43" t="inlineStr">
         <is>
           <t>-</t>
@@ -5632,7 +5636,11 @@
           <t>Shares issued for cash 5</t>
         </is>
       </c>
-      <c r="D51" t="inlineStr"/>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E51" s="5" t="n">
         <v>0.17</v>
       </c>
